--- a/FLORES DE ESTRADA/Diciembre/RESUMEN-Diciembre-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Diciembre/RESUMEN-Diciembre-ESTRADA.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\FLORES DE ESTRADA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E2604E-4259-479C-826F-80429799FA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31582FD5-2F95-4B49-A1A4-6DC5DF2664D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -159,10 +159,16 @@
     <t>Egresos gastos del mes - DICIEMBRE EXTRAORDINARIO</t>
   </si>
   <si>
-    <t>Alterini Guido - Mantenimiento y Alocacia - Mes de NOVIEMBRE - Jardineria</t>
-  </si>
-  <si>
-    <t>Cabie</t>
+    <t>Alterini Guido -Mes de NOVIEMBRE - Jardineria</t>
+  </si>
+  <si>
+    <t>Renovacion anual de cable</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Seguro Sra. Fernanda - Accidentes personales - Poliza Nro. 0043781</t>
   </si>
 </sst>
 </file>
@@ -175,7 +181,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,14 +266,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -465,7 +463,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -513,22 +511,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -547,22 +529,35 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -900,16 +895,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="24"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -919,7 +914,7 @@
       <c r="G1" s="25"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -933,7 +928,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -947,7 +942,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -961,7 +956,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -973,7 +968,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -983,7 +978,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
@@ -997,7 +992,7 @@
       <c r="G7" s="31"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -1007,7 +1002,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="26"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>6</v>
       </c>
@@ -1021,7 +1016,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>8</v>
       </c>
@@ -1035,7 +1030,7 @@
       <c r="G10" s="8"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1045,275 +1040,278 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="56" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40">
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47">
         <f>218000+218000*10%</f>
         <v>239800</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="40"/>
-    </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="47">
+        <f>H13/2</f>
+        <v>119900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42">
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50">
         <f>SUM(H13:H14)</f>
-        <v>239800</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="57" t="s">
+        <v>359700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="43">
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="51">
         <v>31461.68</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="52">
         <f>SUM(H17:H17)</f>
         <v>31461.68</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="57" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="45" t="s">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="46">
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="39" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="43"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="39" t="s">
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="51"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="47">
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="55">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="59" t="s">
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="43">
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="51">
         <v>70000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="43">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="61" t="s">
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="51">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="62">
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="51">
         <v>200000</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="43">
-        <v>55400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="41" t="s">
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="51"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44">
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="52">
         <f>SUM(H24:H27)</f>
-        <v>425400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="39" t="s">
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39" t="s">
+      <c r="B30" s="46"/>
+      <c r="C30" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39" t="s">
+      <c r="D30" s="46"/>
+      <c r="E30" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="41" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="50">
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="60">
         <v>156900</v>
       </c>
       <c r="I31" s="20"/>
@@ -1321,64 +1319,64 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="39" t="s">
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="37">
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="61">
         <v>99656</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="61">
+        <v>7486.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="38">
-        <f>H33+H31+H28+H22+H18+H15</f>
-        <v>953217.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="38">
+        <f>H33+H31+H28+H22+H18+H15+H34</f>
+        <v>1005203.7400000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="34" t="s">
         <v>32</v>
-      </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
-        <v>29</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -1386,99 +1384,99 @@
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
       <c r="G36" s="34"/>
-      <c r="H36" s="35">
-        <f>H34+H35</f>
-        <v>953217.68</v>
-      </c>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="60" t="str">
+      <c r="H36" s="35"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="35">
+        <f>H35+H36</f>
+        <v>1005203.7400000001</v>
+      </c>
+      <c r="I37" s="23"/>
+    </row>
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="52" t="s">
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="33"/>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="55"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="40"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="41"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="16">
-        <v>4383954.5040805172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="16">
+        <v>4653806.8540805168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="18">
-        <v>1141886.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1486,12 +1484,13 @@
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="19"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H44" s="18">
+        <v>1141886.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -1499,14 +1498,12 @@
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
-      <c r="H45" s="13">
-        <f>-( H34 )</f>
-        <v>-953217.68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H45" s="37"/>
+      <c r="I45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1514,100 +1511,115 @@
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A47" s="14" t="s">
+      <c r="H46" s="13">
+        <f>-( H35 )</f>
+        <v>-1005203.7400000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="17">
-        <f>SUM(H42:H46)</f>
-        <v>4572623.3240805175</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="17">
+        <f>SUM(H43:H47)</f>
+        <v>4790489.6140805166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="51"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
-      <c r="G54" s="51"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
       <c r="H54" s="8"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="8"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B49:G54"/>
-    <mergeCell ref="A38:H39"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="B50:G55"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
@@ -1616,7 +1628,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
